--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484715_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484715_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7757</v>
+        <v>3.7832</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3583</v>
+        <v>2.2865</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4174</v>
+        <v>1.4967</v>
       </c>
       <c r="G2" t="n">
         <v>2.8706</v>
@@ -610,13 +610,13 @@
         <v>0.7548</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9993</v>
+        <v>0.0069</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1257</v>
+        <v>0.0539</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1264</v>
+        <v>-0.047</v>
       </c>
       <c r="V2" t="n">
         <v>1.2832</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4357</v>
+        <v>2.9069</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4252</v>
+        <v>5.7377</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9895</v>
+        <v>-2.8308</v>
       </c>
       <c r="G3" t="n">
         <v>5.2839</v>
@@ -688,13 +688,13 @@
         <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9429</v>
+        <v>-0.4717</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7055</v>
+        <v>-0.393</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2375</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-2.4714</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1439</v>
+        <v>1.5395</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2437</v>
+        <v>3.6922</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0997</v>
+        <v>-2.1526</v>
       </c>
       <c r="G4" t="n">
         <v>2.0298</v>
@@ -766,13 +766,13 @@
         <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6972</v>
+        <v>-0.3016</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.458</v>
+        <v>-0.0094</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2392</v>
+        <v>-0.2921</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>M. PEREZ DIEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0649</v>
+        <v>0.1476</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1536</v>
+        <v>0.394</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0887</v>
+        <v>-0.2465</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4347</v>
+        <v>0.1216</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2897</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.145</v>
+        <v>1.0263</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5577</v>
+        <v>0.4158</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2569</v>
+        <v>0.169</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6992</v>
+        <v>0.2468</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.877</v>
+        <v>-0.2942</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0329</v>
+        <v>-1.0737</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8442</v>
+        <v>0.7795</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1222</v>
+        <v>-0.3139</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8999</v>
+        <v>-0.0218</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2222</v>
+        <v>-0.2921</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PEREZ DIEZ</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3539</v>
+        <v>-0.5222</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0545</v>
+        <v>-0.2748</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2994</v>
+        <v>-0.2474</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1216</v>
+        <v>-1.4347</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-1.2897</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0263</v>
+        <v>-0.145</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4158</v>
+        <v>-0.5577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.169</v>
+        <v>-1.2569</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2468</v>
+        <v>0.6992</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2942</v>
+        <v>-0.877</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0737</v>
+        <v>-0.0329</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7795</v>
+        <v>-0.8442</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8153</v>
+        <v>0.5351</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4703</v>
+        <v>0.4716</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.345</v>
+        <v>0.0635</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6346</v>
+        <v>-1.0828</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2581</v>
+        <v>0.3467</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3765</v>
+        <v>-1.4295</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9396</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.148</v>
+        <v>-1.5961</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3521</v>
+        <v>-0.7474</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.8488</v>
       </c>
       <c r="V8" t="n">
         <v>0.3208</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6129</v>
+        <v>-2.6696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2881</v>
+        <v>0.152</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9009</v>
+        <v>-2.8215</v>
       </c>
       <c r="G9" t="n">
         <v>-0.08019999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>1.1322</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6649</v>
+        <v>-0.7216</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1357</v>
+        <v>-0.0004</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8006</v>
+        <v>-0.7212</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8678</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9403</v>
+        <v>-2.9647</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.345</v>
+        <v>-2.4223</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5424</v>
       </c>
       <c r="G10" t="n">
         <v>-1.503</v>
@@ -1234,13 +1234,13 @@
         <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0723</v>
+        <v>0.0479</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2968</v>
+        <v>0.2195</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2246</v>
+        <v>-0.1716</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4948</v>
+        <v>-4.2241</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.628</v>
+        <v>-2.9991</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8668</v>
+        <v>-1.2249</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4933</v>
+        <v>-1.7625</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8047</v>
+        <v>-0.9008</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6887</v>
+        <v>-0.8617</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5854</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8764999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1986</v>
+        <v>-1.0353</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8154</v>
+        <v>-1.1772</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9281</v>
+        <v>-1.3507</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8873</v>
+        <v>0.1736</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3774</v>
+        <v>-3.0192</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5661</v>
+        <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6431</v>
+        <v>-1.1972</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5726</v>
+        <v>-0.319</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.8782</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.547</v>
+        <v>0.6226</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5835</v>
+        <v>-4.3675</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2528</v>
+        <v>-1.3155</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3308</v>
+        <v>-3.052</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7625</v>
+        <v>-2.4933</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9008</v>
+        <v>-1.8047</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8617</v>
+        <v>-0.6887</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5854</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.45</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.0353</v>
+        <v>0.1986</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1772</v>
+        <v>-1.8154</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3507</v>
+        <v>-0.9281</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1736</v>
+        <v>-0.8873</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0192</v>
+        <v>-0.3774</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5566</v>
+        <v>-0.5158</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5726</v>
+        <v>-0.2602</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.984</v>
+        <v>-0.2556</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6226</v>
+        <v>-1.547</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3018</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8525</v>
+        <v>-5.7169</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5057</v>
+        <v>-1.2907</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.3468</v>
+        <v>-4.4262</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2794</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9129</v>
+        <v>-0.7773</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5262</v>
+        <v>-0.3112</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3868</v>
+        <v>-0.4661</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4714</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.1184</v>
+        <v>-12.2367</v>
       </c>
       <c r="E14" t="n">
-        <v>4.358699999999998</v>
+        <v>5.240600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.477</v>
+        <v>-17.4771</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7470999999999997</v>
+        <v>0.7470999999999992</v>
       </c>
       <c r="H14" t="n">
         <v>-11.0503</v>
@@ -1537,22 +1537,22 @@
         <v>-1.946</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9434999999999999</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.3785</v>
       </c>
       <c r="R14" t="n">
-        <v>9.435000000000002</v>
+        <v>9.435</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.187100000000001</v>
+        <v>-5.305300000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1992</v>
+        <v>-1.3174</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.9883</v>
+        <v>-3.9879</v>
       </c>
       <c r="V14" t="n">
         <v>-6.734599999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6689</v>
+        <v>8.1427</v>
       </c>
       <c r="E15" t="n">
         <v>8.0707</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4018</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>2.8405</v>
@@ -1624,13 +1624,13 @@
         <v>1.1322</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4891</v>
+        <v>0.9629</v>
       </c>
       <c r="T15" t="n">
         <v>0.9834000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4943</v>
+        <v>-0.0205</v>
       </c>
       <c r="V15" t="n">
         <v>4.3392</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7854</v>
+        <v>5.0398</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4955</v>
+        <v>4.9109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2899</v>
+        <v>0.1289</v>
       </c>
       <c r="G16" t="n">
         <v>0.5054999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>2.884</v>
+        <v>2.1383</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5524</v>
+        <v>0.9678</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3316</v>
+        <v>1.1705</v>
       </c>
       <c r="V16" t="n">
         <v>1.8298</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5479</v>
+        <v>3.7656</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1072</v>
+        <v>3.0098</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4407</v>
+        <v>0.7558</v>
       </c>
       <c r="G17" t="n">
         <v>2.5147</v>
@@ -1780,13 +1780,13 @@
         <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1364</v>
+        <v>0.0813</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4267</v>
+        <v>0.3293</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5631</v>
+        <v>-0.248</v>
       </c>
       <c r="V17" t="n">
         <v>1.547</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>A. VISQUERT MADRID</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5456</v>
+        <v>2.066</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2847</v>
+        <v>1.892</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2608</v>
+        <v>0.174</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4317</v>
+        <v>2.0219</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0745</v>
+        <v>0.1299</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5062</v>
+        <v>1.892</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7616</v>
+        <v>1.892</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9305</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8310999999999999</v>
+        <v>1.892</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1933</v>
+        <v>0.1299</v>
       </c>
       <c r="N18" t="n">
-        <v>0.144</v>
+        <v>0.1299</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.3374</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.0904</v>
+        <v>0.0441</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0328</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0577</v>
+        <v>0.0441</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VISQUERT MADRID</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0395</v>
+        <v>1.3609</v>
       </c>
       <c r="E19" t="n">
-        <v>1.892</v>
+        <v>1.6027</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1475</v>
+        <v>-0.2418</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0219</v>
+        <v>-0.4317</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1299</v>
+        <v>1.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>1.892</v>
+        <v>-1.5062</v>
       </c>
       <c r="J19" t="n">
-        <v>1.892</v>
+        <v>1.7616</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.9305</v>
       </c>
       <c r="L19" t="n">
-        <v>1.892</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1299</v>
+        <v>-2.1933</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1299</v>
+        <v>0.144</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-2.3374</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0176</v>
+        <v>0.9058</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.3507</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0176</v>
+        <v>0.555</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6574</v>
+        <v>1.0547</v>
       </c>
       <c r="E20" t="n">
-        <v>3.7854</v>
+        <v>3.1034</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.128</v>
+        <v>-2.0486</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4132</v>
@@ -2014,13 +2014,13 @@
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8252</v>
+        <v>1.2226</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3267</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4985</v>
+        <v>0.5779</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2642</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4696</v>
+        <v>0.8835</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4554</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.925</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.5795</v>
@@ -2092,13 +2092,13 @@
         <v>0.5661</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1663</v>
+        <v>0.2475</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3527</v>
+        <v>0.037</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1864</v>
+        <v>0.2105</v>
       </c>
       <c r="V21" t="n">
         <v>0.6226</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5911</v>
+        <v>-0.3085</v>
       </c>
       <c r="E22" t="n">
-        <v>0.419</v>
+        <v>0.5164</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0101</v>
+        <v>-0.8249</v>
       </c>
       <c r="G22" t="n">
         <v>0.1556</v>
@@ -2170,13 +2170,13 @@
         <v>0.3774</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5014</v>
+        <v>-0.2188</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0247</v>
+        <v>0.1221</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5261</v>
+        <v>-0.3409</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7743</v>
+        <v>-3.6941</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.717</v>
+        <v>-2.7427</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0572</v>
+        <v>-0.9514</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2249</v>
@@ -2248,13 +2248,13 @@
         <v>1.5096</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4738</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6684</v>
+        <v>0.3059</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1947</v>
+        <v>0.3005</v>
       </c>
       <c r="V23" t="n">
         <v>0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2306</v>
+        <v>-4.5426</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.405</v>
+        <v>-2.8204</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8257</v>
+        <v>-1.7222</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2948</v>
@@ -2326,13 +2326,13 @@
         <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1587</v>
+        <v>0.8468</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3375</v>
+        <v>0.2471</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4962</v>
+        <v>0.5997</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3398</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.1183</v>
+        <v>13.768</v>
       </c>
       <c r="E25" t="n">
-        <v>17.4771</v>
+        <v>17.4772</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.3589</v>
+        <v>-3.7091</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7469000000000001</v>
@@ -2404,16 +2404,16 @@
         <v>10.3785</v>
       </c>
       <c r="S25" t="n">
-        <v>6.1871</v>
+        <v>6.8369</v>
       </c>
       <c r="T25" t="n">
-        <v>3.9881</v>
+        <v>3.988</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1992</v>
+        <v>2.8488</v>
       </c>
       <c r="V25" t="n">
-        <v>6.734599999999999</v>
+        <v>6.7346</v>
       </c>
       <c r="W25" t="n">
         <v>11.3756</v>
